--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="976">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3902,17 +3902,20 @@
   <si>
     <t>крепление для ппр труб 16 (10шт упак) 2 упак</t>
   </si>
+  <si>
+    <t>Регулятор напряжения и мощности, диммер 220V 4000 Вт (4 кВт)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4206,6 +4209,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF070707"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4258,17 +4269,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4282,9 +4293,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4322,11 +4333,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4371,13 +4382,16 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -4390,7 +4404,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4401,7 +4415,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4410,7 +4424,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4443,49 +4457,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4512,10 +4526,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4596,7 +4610,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -17406,8 +17420,18 @@
       </c>
     </row>
     <row r="572" spans="3:6">
-      <c r="D572" s="7"/>
-      <c r="F572" s="9"/>
+      <c r="C572" s="65" t="s">
+        <v>975</v>
+      </c>
+      <c r="D572" s="7">
+        <v>280</v>
+      </c>
+      <c r="E572" t="s">
+        <v>372</v>
+      </c>
+      <c r="F572" s="9">
+        <v>46275</v>
+      </c>
     </row>
     <row r="573" spans="3:6">
       <c r="D573" s="7"/>
@@ -17448,7 +17472,7 @@
     <row r="582" spans="4:6">
       <c r="D582" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6411532.2200000016</v>
+        <v>6411812.2200000016</v>
       </c>
       <c r="F582" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="990">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3905,15 +3905,57 @@
   <si>
     <t>Регулятор напряжения и мощности, диммер 220V 4000 Вт (4 кВт)</t>
   </si>
+  <si>
+    <t xml:space="preserve">очиститель незатвердевшей монтажной пены 500 мл Технониколь </t>
+  </si>
+  <si>
+    <t>клей пена монтажная профессионал 500 - 1000 мл Технониколь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">стажка кабельная 2,5 х 169мм черная 100 шт safeline </t>
+  </si>
+  <si>
+    <t xml:space="preserve">дюбель хомут 10/5 плоский черный 50 шт ekf </t>
+  </si>
+  <si>
+    <t xml:space="preserve">площадка под стяжку компакт 16х23  белая 100шт / упак dynel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">дюбель хомут 14/6 плоский черный 50 шт ekf </t>
+  </si>
+  <si>
+    <t xml:space="preserve">скобы тип 140 12мм 1000шт dorn </t>
+  </si>
+  <si>
+    <t>Коронка по бетону SDS-Plus 80мм с хвостовиком DORN (для коробок расключения )</t>
+  </si>
+  <si>
+    <t>ИП Зверев Электроцентр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кабель ввгп-нг ls 3x2,5 мм2 - 50 метров; гофра труба пвх 100 метров; </t>
+  </si>
+  <si>
+    <t>дюбель хомут; стяжки</t>
+  </si>
+  <si>
+    <t>Труба гофрированная ПВХ 25мм с/з 15м IEK</t>
+  </si>
+  <si>
+    <t>кабель ВВГ нг(А) ls 5x4 mm2 круглый 8 метров</t>
+  </si>
+  <si>
+    <t>кабель ВВГ-пнг-ls 3х2,5 мм2 50 метров</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4269,17 +4311,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4293,9 +4335,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4333,11 +4375,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4382,9 +4424,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4404,7 +4446,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4415,7 +4457,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4424,7 +4466,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4457,49 +4499,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4526,10 +4568,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4610,7 +4652,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4883,8 +4925,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F582" totalsRowCount="1">
-  <autoFilter ref="B5:F581"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F607" totalsRowCount="1">
+  <autoFilter ref="B5:F606"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -7825,7 +7867,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I582"/>
+  <dimension ref="B3:I607"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="94.7109375" customWidth="1"/>
@@ -17434,47 +17476,287 @@
       </c>
     </row>
     <row r="573" spans="3:6">
-      <c r="D573" s="7"/>
-      <c r="F573" s="9"/>
+      <c r="C573" t="s">
+        <v>976</v>
+      </c>
+      <c r="D573" s="7">
+        <v>160.41999999999999</v>
+      </c>
+      <c r="E573" t="s">
+        <v>885</v>
+      </c>
+      <c r="F573" s="9">
+        <v>46282</v>
+      </c>
     </row>
     <row r="574" spans="3:6">
-      <c r="D574" s="7"/>
-      <c r="F574" s="9"/>
+      <c r="C574" t="s">
+        <v>977</v>
+      </c>
+      <c r="D574" s="7">
+        <v>594.73</v>
+      </c>
+      <c r="E574" t="s">
+        <v>885</v>
+      </c>
+      <c r="F574" s="9">
+        <v>46282</v>
+      </c>
     </row>
     <row r="575" spans="3:6">
-      <c r="D575" s="7"/>
-      <c r="F575" s="9"/>
+      <c r="C575" t="s">
+        <v>978</v>
+      </c>
+      <c r="D575" s="7">
+        <v>105.08</v>
+      </c>
+      <c r="E575" t="s">
+        <v>885</v>
+      </c>
+      <c r="F575" s="9">
+        <v>46282</v>
+      </c>
     </row>
     <row r="576" spans="3:6">
-      <c r="D576" s="7"/>
-      <c r="F576" s="9"/>
-    </row>
-    <row r="577" spans="4:6">
-      <c r="D577" s="7"/>
-      <c r="F577" s="9"/>
-    </row>
-    <row r="578" spans="4:6">
-      <c r="D578" s="7"/>
-      <c r="F578" s="9"/>
-    </row>
-    <row r="579" spans="4:6">
-      <c r="D579" s="7"/>
-      <c r="F579" s="9"/>
-    </row>
-    <row r="580" spans="4:6">
-      <c r="D580" s="7"/>
-      <c r="F580" s="9"/>
-    </row>
-    <row r="581" spans="4:6">
-      <c r="D581" s="7"/>
-      <c r="F581" s="9"/>
-    </row>
-    <row r="582" spans="4:6">
+      <c r="C576" t="s">
+        <v>979</v>
+      </c>
+      <c r="D576" s="7">
+        <v>58.14</v>
+      </c>
+      <c r="E576" t="s">
+        <v>885</v>
+      </c>
+      <c r="F576" s="9">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="577" spans="3:6">
+      <c r="C577" t="s">
+        <v>980</v>
+      </c>
+      <c r="D577" s="7">
+        <v>139.4</v>
+      </c>
+      <c r="E577" t="s">
+        <v>885</v>
+      </c>
+      <c r="F577" s="9">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="578" spans="3:6">
+      <c r="C578" t="s">
+        <v>981</v>
+      </c>
+      <c r="D578" s="7">
+        <v>72.849999999999994</v>
+      </c>
+      <c r="E578" t="s">
+        <v>885</v>
+      </c>
+      <c r="F578" s="9">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="579" spans="3:6">
+      <c r="C579" t="s">
+        <v>982</v>
+      </c>
+      <c r="D579" s="7">
+        <v>104.38</v>
+      </c>
+      <c r="E579" t="s">
+        <v>885</v>
+      </c>
+      <c r="F579" s="9">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="580" spans="3:6">
+      <c r="C580" t="s">
+        <v>977</v>
+      </c>
+      <c r="D580" s="7">
+        <v>594.49</v>
+      </c>
+      <c r="E580" t="s">
+        <v>885</v>
+      </c>
+      <c r="F580" s="9">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="581" spans="3:6">
+      <c r="C581" t="s">
+        <v>983</v>
+      </c>
+      <c r="D581" s="7">
+        <v>664.51</v>
+      </c>
+      <c r="E581" t="s">
+        <v>885</v>
+      </c>
+      <c r="F581" s="9">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="582" spans="3:6">
+      <c r="C582" t="s">
+        <v>986</v>
+      </c>
       <c r="D582" s="7">
+        <v>494</v>
+      </c>
+      <c r="E582" t="s">
+        <v>984</v>
+      </c>
+      <c r="F582" s="9">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="583" spans="3:6">
+      <c r="C583" t="s">
+        <v>985</v>
+      </c>
+      <c r="D583" s="7">
+        <v>12764.02</v>
+      </c>
+      <c r="E583" t="s">
+        <v>964</v>
+      </c>
+      <c r="F583" s="9">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="584" spans="3:6">
+      <c r="C584" t="s">
+        <v>987</v>
+      </c>
+      <c r="D584" s="7">
+        <v>669.3</v>
+      </c>
+      <c r="E584" t="s">
+        <v>964</v>
+      </c>
+      <c r="F584" s="9">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="585" spans="3:6">
+      <c r="C585" t="s">
+        <v>988</v>
+      </c>
+      <c r="D585" s="7">
+        <v>3492</v>
+      </c>
+      <c r="E585" t="s">
+        <v>964</v>
+      </c>
+      <c r="F585" s="9">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="586" spans="3:6">
+      <c r="C586" t="s">
+        <v>989</v>
+      </c>
+      <c r="D586" s="7">
+        <v>5995</v>
+      </c>
+      <c r="E586" t="s">
+        <v>964</v>
+      </c>
+      <c r="F586" s="9">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="587" spans="3:6">
+      <c r="D587" s="7"/>
+      <c r="F587" s="9"/>
+    </row>
+    <row r="588" spans="3:6">
+      <c r="D588" s="7"/>
+      <c r="F588" s="9"/>
+    </row>
+    <row r="589" spans="3:6">
+      <c r="D589" s="7"/>
+      <c r="F589" s="9"/>
+    </row>
+    <row r="590" spans="3:6">
+      <c r="D590" s="7"/>
+      <c r="F590" s="9"/>
+    </row>
+    <row r="591" spans="3:6">
+      <c r="D591" s="7"/>
+      <c r="F591" s="9"/>
+    </row>
+    <row r="592" spans="3:6">
+      <c r="D592" s="7"/>
+      <c r="F592" s="9"/>
+    </row>
+    <row r="593" spans="4:6">
+      <c r="D593" s="7"/>
+      <c r="F593" s="9"/>
+    </row>
+    <row r="594" spans="4:6">
+      <c r="D594" s="7"/>
+      <c r="F594" s="9"/>
+    </row>
+    <row r="595" spans="4:6">
+      <c r="D595" s="7"/>
+      <c r="F595" s="9"/>
+    </row>
+    <row r="596" spans="4:6">
+      <c r="D596" s="7"/>
+      <c r="F596" s="9"/>
+    </row>
+    <row r="597" spans="4:6">
+      <c r="D597" s="7"/>
+      <c r="F597" s="9"/>
+    </row>
+    <row r="598" spans="4:6">
+      <c r="D598" s="7"/>
+      <c r="F598" s="9"/>
+    </row>
+    <row r="599" spans="4:6">
+      <c r="D599" s="7"/>
+      <c r="F599" s="9"/>
+    </row>
+    <row r="600" spans="4:6">
+      <c r="D600" s="7"/>
+      <c r="F600" s="9"/>
+    </row>
+    <row r="601" spans="4:6">
+      <c r="D601" s="7"/>
+      <c r="F601" s="9"/>
+    </row>
+    <row r="602" spans="4:6">
+      <c r="D602" s="7"/>
+      <c r="F602" s="9"/>
+    </row>
+    <row r="603" spans="4:6">
+      <c r="D603" s="7"/>
+      <c r="F603" s="9"/>
+    </row>
+    <row r="604" spans="4:6">
+      <c r="D604" s="7"/>
+      <c r="F604" s="9"/>
+    </row>
+    <row r="605" spans="4:6">
+      <c r="D605" s="7"/>
+      <c r="F605" s="9"/>
+    </row>
+    <row r="606" spans="4:6">
+      <c r="D606" s="7"/>
+      <c r="F606" s="9"/>
+    </row>
+    <row r="607" spans="4:6">
+      <c r="D607" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6411812.2200000016</v>
-      </c>
-      <c r="F582" s="9"/>
+        <v>6437720.540000001</v>
+      </c>
+      <c r="F607" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="994">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3933,12 +3933,6 @@
     <t>ИП Зверев Электроцентр</t>
   </si>
   <si>
-    <t xml:space="preserve">кабель ввгп-нг ls 3x2,5 мм2 - 50 метров; гофра труба пвх 100 метров; </t>
-  </si>
-  <si>
-    <t>дюбель хомут; стяжки</t>
-  </si>
-  <si>
     <t>Труба гофрированная ПВХ 25мм с/з 15м IEK</t>
   </si>
   <si>
@@ -3946,16 +3940,34 @@
   </si>
   <si>
     <t>кабель ВВГ-пнг-ls 3х2,5 мм2 50 метров</t>
+  </si>
+  <si>
+    <t>коробка распределительная с/п 80(100) 17 шт; хомут 4,8*200 чёрный UV нейлон 100шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">кабель ввгп-нг ls 3x2,5 мм2 - 50 метров; кабель ввгп-нг ls 3x1,5 мм2 - 50 метров;дюбель хомут дхп 14х6мм 100шт; </t>
+  </si>
+  <si>
+    <t>ИП Савельев Электроцентр 3x2,5 мм2 - 50 метров - 5995р; кабель 3x1,5 мм2 - 50 метров-3795р;</t>
+  </si>
+  <si>
+    <t>кабель комп. CAT5E electroline 200 м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">коробка распред с крышкой с сплошн стены 80мм лаптаупласт 12 шт </t>
+  </si>
+  <si>
+    <t>перчатки полиэстер 2 пар</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4311,17 +4323,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4335,9 +4347,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4375,11 +4387,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4424,9 +4436,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4446,7 +4458,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4457,7 +4469,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4466,7 +4478,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4499,49 +4511,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4568,10 +4580,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4652,7 +4664,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -7870,7 +7882,7 @@
   <dimension ref="B3:I607"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="94.7109375" customWidth="1"/>
+    <col min="3" max="3" width="103.5703125" customWidth="1"/>
     <col min="4" max="4" width="22.5703125" customWidth="1"/>
     <col min="5" max="5" width="90.85546875" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -17603,7 +17615,7 @@
     </row>
     <row r="582" spans="3:6">
       <c r="C582" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D582" s="7">
         <v>494</v>
@@ -17617,13 +17629,13 @@
     </row>
     <row r="583" spans="3:6">
       <c r="C583" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D583" s="7">
         <v>12764.02</v>
       </c>
       <c r="E583" t="s">
-        <v>964</v>
+        <v>990</v>
       </c>
       <c r="F583" s="9">
         <v>46287</v>
@@ -17631,7 +17643,7 @@
     </row>
     <row r="584" spans="3:6">
       <c r="C584" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D584" s="7">
         <v>669.3</v>
@@ -17645,7 +17657,7 @@
     </row>
     <row r="585" spans="3:6">
       <c r="C585" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="D585" s="7">
         <v>3492</v>
@@ -17659,7 +17671,7 @@
     </row>
     <row r="586" spans="3:6">
       <c r="C586" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="D586" s="7">
         <v>5995</v>
@@ -17672,15 +17684,36 @@
       </c>
     </row>
     <row r="587" spans="3:6">
-      <c r="D587" s="7"/>
-      <c r="F587" s="9"/>
+      <c r="C587" t="s">
+        <v>991</v>
+      </c>
+      <c r="D587" s="7">
+        <v>9666.2000000000007</v>
+      </c>
+      <c r="E587" t="s">
+        <v>885</v>
+      </c>
+      <c r="F587" s="9">
+        <v>46291</v>
+      </c>
     </row>
     <row r="588" spans="3:6">
-      <c r="D588" s="7"/>
+      <c r="C588" t="s">
+        <v>992</v>
+      </c>
+      <c r="D588" s="7">
+        <v>177.55</v>
+      </c>
       <c r="F588" s="9"/>
     </row>
     <row r="589" spans="3:6">
-      <c r="D589" s="7"/>
+      <c r="C589" t="s">
+        <v>993</v>
+      </c>
+      <c r="D589" s="7">
+        <f>77.92*2</f>
+        <v>155.84</v>
+      </c>
       <c r="F589" s="9"/>
     </row>
     <row r="590" spans="3:6">
@@ -17754,7 +17787,7 @@
     <row r="607" spans="4:6">
       <c r="D607" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6437720.540000001</v>
+        <v>6447720.1300000008</v>
       </c>
       <c r="F607" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="994">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3946,6 +3946,18 @@
   </si>
   <si>
     <t>кабель ВВГ-пнг-ls 3х2,5 мм2 50 метров</t>
+  </si>
+  <si>
+    <t xml:space="preserve">щётка смётка econova </t>
+  </si>
+  <si>
+    <t xml:space="preserve">совок пластиковый </t>
+  </si>
+  <si>
+    <t>кабель твёрдый плоский ввгп-нг-ls 3x2,5 мм2 50 метров ПРОМЭКО</t>
+  </si>
+  <si>
+    <t>Маркер разметочный 3мм чёрный 2 шт</t>
   </si>
 </sst>
 </file>
@@ -17672,24 +17684,74 @@
       </c>
     </row>
     <row r="587" spans="3:6">
-      <c r="D587" s="7"/>
-      <c r="F587" s="9"/>
+      <c r="C587" t="s">
+        <v>990</v>
+      </c>
+      <c r="D587" s="7">
+        <v>136.41999999999999</v>
+      </c>
+      <c r="E587" t="s">
+        <v>885</v>
+      </c>
+      <c r="F587" s="9">
+        <v>46294</v>
+      </c>
     </row>
     <row r="588" spans="3:6">
-      <c r="D588" s="7"/>
-      <c r="F588" s="9"/>
+      <c r="C588" t="s">
+        <v>991</v>
+      </c>
+      <c r="D588" s="7">
+        <v>54.02</v>
+      </c>
+      <c r="E588" t="s">
+        <v>885</v>
+      </c>
+      <c r="F588" s="9">
+        <v>46294</v>
+      </c>
     </row>
     <row r="589" spans="3:6">
-      <c r="D589" s="7"/>
-      <c r="F589" s="9"/>
+      <c r="C589" t="s">
+        <v>992</v>
+      </c>
+      <c r="D589" s="7">
+        <v>5392.6</v>
+      </c>
+      <c r="E589" t="s">
+        <v>885</v>
+      </c>
+      <c r="F589" s="9">
+        <v>46294</v>
+      </c>
     </row>
     <row r="590" spans="3:6">
-      <c r="D590" s="7"/>
-      <c r="F590" s="9"/>
+      <c r="C590" t="s">
+        <v>993</v>
+      </c>
+      <c r="D590" s="7">
+        <v>53.1</v>
+      </c>
+      <c r="E590" t="s">
+        <v>885</v>
+      </c>
+      <c r="F590" s="9">
+        <v>46294</v>
+      </c>
     </row>
     <row r="591" spans="3:6">
-      <c r="D591" s="7"/>
-      <c r="F591" s="9"/>
+      <c r="C591" t="s">
+        <v>163</v>
+      </c>
+      <c r="D591" s="7">
+        <v>46.86</v>
+      </c>
+      <c r="E591" t="s">
+        <v>885</v>
+      </c>
+      <c r="F591" s="9">
+        <v>46294</v>
+      </c>
     </row>
     <row r="592" spans="3:6">
       <c r="D592" s="7"/>
@@ -17754,7 +17816,7 @@
     <row r="607" spans="4:6">
       <c r="D607" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6437720.540000001</v>
+        <v>6443403.54</v>
       </c>
       <c r="F607" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="999">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3959,15 +3959,30 @@
   <si>
     <t>Маркер разметочный 3мм чёрный 2 шт</t>
   </si>
+  <si>
+    <t xml:space="preserve">полумаска изолирующая исток -300/400 с фильтрами А1Р1 </t>
+  </si>
+  <si>
+    <t>фильтр комбинированный к полумаске исток 300/400 а1р1 2 шт в упак</t>
+  </si>
+  <si>
+    <t>кабель твёрдый плоский ввгп-нг-ls 3x2,5 мм2 20 метров ПРОМЭКО</t>
+  </si>
+  <si>
+    <t>Труба гофрированная ПВХ "легкая" 20мм с/з 25м Эра</t>
+  </si>
+  <si>
+    <t>угловая шлифмашинка 150мм 1500 Вт регул оборотов HAG15150EC hanskonner</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4323,17 +4338,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4347,9 +4362,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4387,11 +4402,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4436,9 +4451,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4458,7 +4473,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4469,7 +4484,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4478,7 +4493,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4511,49 +4526,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4580,10 +4595,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4664,7 +4679,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4937,8 +4952,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F607" totalsRowCount="1">
-  <autoFilter ref="B5:F606"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F612" totalsRowCount="1">
+  <autoFilter ref="B5:F611"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -7879,7 +7894,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I607"/>
+  <dimension ref="B3:I612"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="94.7109375" customWidth="1"/>
@@ -17754,71 +17769,141 @@
       </c>
     </row>
     <row r="592" spans="3:6">
-      <c r="D592" s="7"/>
-      <c r="F592" s="9"/>
-    </row>
-    <row r="593" spans="4:6">
-      <c r="D593" s="7"/>
-      <c r="F593" s="9"/>
-    </row>
-    <row r="594" spans="4:6">
-      <c r="D594" s="7"/>
-      <c r="F594" s="9"/>
-    </row>
-    <row r="595" spans="4:6">
-      <c r="D595" s="7"/>
-      <c r="F595" s="9"/>
-    </row>
-    <row r="596" spans="4:6">
-      <c r="D596" s="7"/>
-      <c r="F596" s="9"/>
-    </row>
-    <row r="597" spans="4:6">
+      <c r="C592" t="s">
+        <v>994</v>
+      </c>
+      <c r="D592" s="7">
+        <v>452.07</v>
+      </c>
+      <c r="E592" t="s">
+        <v>885</v>
+      </c>
+      <c r="F592" s="9">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="593" spans="3:6">
+      <c r="C593" t="s">
+        <v>995</v>
+      </c>
+      <c r="D593" s="7">
+        <v>363.43</v>
+      </c>
+      <c r="E593" t="s">
+        <v>885</v>
+      </c>
+      <c r="F593" s="9">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="594" spans="3:6">
+      <c r="C594" t="s">
+        <v>996</v>
+      </c>
+      <c r="D594" s="7">
+        <v>2550.87</v>
+      </c>
+      <c r="E594" t="s">
+        <v>885</v>
+      </c>
+      <c r="F594" s="9">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="595" spans="3:6">
+      <c r="C595" t="s">
+        <v>997</v>
+      </c>
+      <c r="D595" s="7">
+        <v>609.65</v>
+      </c>
+      <c r="E595" t="s">
+        <v>885</v>
+      </c>
+      <c r="F595" s="9">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="596" spans="3:6">
+      <c r="C596" t="s">
+        <v>998</v>
+      </c>
+      <c r="D596" s="7">
+        <v>10823</v>
+      </c>
+      <c r="E596" t="s">
+        <v>885</v>
+      </c>
+      <c r="F596" s="9">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="597" spans="3:6">
       <c r="D597" s="7"/>
       <c r="F597" s="9"/>
     </row>
-    <row r="598" spans="4:6">
+    <row r="598" spans="3:6">
       <c r="D598" s="7"/>
       <c r="F598" s="9"/>
     </row>
-    <row r="599" spans="4:6">
+    <row r="599" spans="3:6">
       <c r="D599" s="7"/>
       <c r="F599" s="9"/>
     </row>
-    <row r="600" spans="4:6">
+    <row r="600" spans="3:6">
       <c r="D600" s="7"/>
       <c r="F600" s="9"/>
     </row>
-    <row r="601" spans="4:6">
+    <row r="601" spans="3:6">
       <c r="D601" s="7"/>
       <c r="F601" s="9"/>
     </row>
-    <row r="602" spans="4:6">
+    <row r="602" spans="3:6">
       <c r="D602" s="7"/>
       <c r="F602" s="9"/>
     </row>
-    <row r="603" spans="4:6">
+    <row r="603" spans="3:6">
       <c r="D603" s="7"/>
       <c r="F603" s="9"/>
     </row>
-    <row r="604" spans="4:6">
+    <row r="604" spans="3:6">
       <c r="D604" s="7"/>
       <c r="F604" s="9"/>
     </row>
-    <row r="605" spans="4:6">
+    <row r="605" spans="3:6">
       <c r="D605" s="7"/>
       <c r="F605" s="9"/>
     </row>
-    <row r="606" spans="4:6">
+    <row r="606" spans="3:6">
       <c r="D606" s="7"/>
       <c r="F606" s="9"/>
     </row>
-    <row r="607" spans="4:6">
-      <c r="D607" s="7">
+    <row r="607" spans="3:6">
+      <c r="D607" s="7"/>
+      <c r="F607" s="9"/>
+    </row>
+    <row r="608" spans="3:6">
+      <c r="D608" s="7"/>
+      <c r="F608" s="9"/>
+    </row>
+    <row r="609" spans="4:6">
+      <c r="D609" s="7"/>
+      <c r="F609" s="9"/>
+    </row>
+    <row r="610" spans="4:6">
+      <c r="D610" s="7"/>
+      <c r="F610" s="9"/>
+    </row>
+    <row r="611" spans="4:6">
+      <c r="D611" s="7"/>
+      <c r="F611" s="9"/>
+    </row>
+    <row r="612" spans="4:6">
+      <c r="D612" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6443403.54</v>
-      </c>
-      <c r="F607" s="9"/>
+        <v>6458202.5600000005</v>
+      </c>
+      <c r="F612" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="1001">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3974,15 +3974,21 @@
   <si>
     <t>угловая шлифмашинка 150мм 1500 Вт регул оборотов HAG15150EC hanskonner</t>
   </si>
+  <si>
+    <t xml:space="preserve">стальной лист 0.2х125х250 см + 2 полосы п 6 м.  </t>
+  </si>
+  <si>
+    <t>КСМ39, ООО СИТ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4338,17 +4344,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4362,9 +4368,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4402,11 +4408,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4451,9 +4457,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4473,7 +4479,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4484,7 +4490,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4493,7 +4499,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4526,49 +4532,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4595,10 +4601,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4679,7 +4685,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -17839,8 +17845,18 @@
       </c>
     </row>
     <row r="597" spans="3:6">
-      <c r="D597" s="7"/>
-      <c r="F597" s="9"/>
+      <c r="C597" t="s">
+        <v>999</v>
+      </c>
+      <c r="D597" s="7">
+        <v>5665</v>
+      </c>
+      <c r="E597" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F597" s="9">
+        <v>46298</v>
+      </c>
     </row>
     <row r="598" spans="3:6">
       <c r="D598" s="7"/>
@@ -17901,7 +17917,7 @@
     <row r="612" spans="4:6">
       <c r="D612" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6458202.5600000005</v>
+        <v>6463867.5600000005</v>
       </c>
       <c r="F612" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -3978,17 +3978,17 @@
     <t xml:space="preserve">стальной лист 0.2х125х250 см + 2 полосы п 6 м.  </t>
   </si>
   <si>
-    <t>КСМ39, ООО СИТ</t>
+    <t>КСМ39, ООО СИТ лист ГК 2х1250х2500 мм - 4100Р; полоса 25х4х6000мм 2шт - 1040р</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4344,17 +4344,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4368,9 +4368,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4408,11 +4408,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4457,9 +4457,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4479,7 +4479,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4490,7 +4490,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4499,7 +4499,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4532,49 +4532,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4601,10 +4601,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4685,7 +4685,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="1007">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3980,15 +3980,33 @@
   <si>
     <t>КСМ39, ООО СИТ лист ГК 2х1250х2500 мм - 4100Р; полоса 25х4х6000мм 2шт - 1040р</t>
   </si>
+  <si>
+    <t>Воздуховод круглый пластиковый 100 мм х 1 м 10ВП1 ERA</t>
+  </si>
+  <si>
+    <t>Воздуховод круглый пластиковый 100 мм х 1,5 м 10ВП1,5 ERA</t>
+  </si>
+  <si>
+    <t>соединитель фасонных элементов (отрезок канала) fc d100 пластик ЭРА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">гильза медная лужённая гмл 6-4 10 шт </t>
+  </si>
+  <si>
+    <t xml:space="preserve">гильза медная лужённая гмл 10-5 10 шт </t>
+  </si>
+  <si>
+    <t>труба металопластиковая pex-al-pex 20x2.0 valtec 50 метров</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4344,17 +4362,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4368,9 +4386,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4408,11 +4426,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4457,9 +4475,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4479,7 +4497,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4490,7 +4508,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4499,7 +4517,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4532,49 +4550,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4601,10 +4619,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4685,7 +4703,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -17859,28 +17877,89 @@
       </c>
     </row>
     <row r="598" spans="3:6">
-      <c r="D598" s="7"/>
-      <c r="F598" s="9"/>
+      <c r="C598" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D598" s="7">
+        <v>507.98</v>
+      </c>
+      <c r="E598" t="s">
+        <v>885</v>
+      </c>
+      <c r="F598" s="9">
+        <v>46304</v>
+      </c>
     </row>
     <row r="599" spans="3:6">
-      <c r="D599" s="7"/>
-      <c r="F599" s="9"/>
+      <c r="C599" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D599" s="7">
+        <v>536.25</v>
+      </c>
+      <c r="E599" t="s">
+        <v>885</v>
+      </c>
+      <c r="F599" s="9">
+        <v>46304</v>
+      </c>
     </row>
     <row r="600" spans="3:6">
-      <c r="D600" s="7"/>
-      <c r="F600" s="9"/>
+      <c r="C600" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D600" s="7">
+        <v>84.82</v>
+      </c>
+      <c r="E600" t="s">
+        <v>885</v>
+      </c>
+      <c r="F600" s="9">
+        <v>46304</v>
+      </c>
     </row>
     <row r="601" spans="3:6">
-      <c r="D601" s="7"/>
-      <c r="F601" s="9"/>
+      <c r="C601" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D601" s="7">
+        <v>206.4</v>
+      </c>
+      <c r="E601" t="s">
+        <v>885</v>
+      </c>
+      <c r="F601" s="9">
+        <v>46304</v>
+      </c>
     </row>
     <row r="602" spans="3:6">
-      <c r="D602" s="7"/>
-      <c r="F602" s="9"/>
+      <c r="C602" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D602" s="7">
+        <v>300.64</v>
+      </c>
+      <c r="E602" t="s">
+        <v>885</v>
+      </c>
+      <c r="F602" s="9">
+        <v>46304</v>
+      </c>
     </row>
     <row r="603" spans="3:6">
-      <c r="D603" s="7"/>
-      <c r="F603" s="9"/>
+      <c r="C603" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D603" s="7">
+        <f>6607.56+1450.35</f>
+        <v>8057.91</v>
+      </c>
+      <c r="E603" t="s">
+        <v>885</v>
+      </c>
+      <c r="F603" s="9">
+        <v>46304</v>
+      </c>
     </row>
     <row r="604" spans="3:6">
       <c r="D604" s="7"/>
@@ -17917,7 +17996,7 @@
     <row r="612" spans="4:6">
       <c r="D612" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6463867.5600000005</v>
+        <v>6473561.5600000015</v>
       </c>
       <c r="F612" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="1009">
   <si>
     <t>№ п/п</t>
   </si>
@@ -3997,6 +3997,12 @@
   </si>
   <si>
     <t>труба металопластиковая pex-al-pex 20x2.0 valtec 50 метров</t>
+  </si>
+  <si>
+    <t>ООО "Контур Лидер" контуртерм</t>
+  </si>
+  <si>
+    <t>котёл газовый двухконтурный Haier TechLine S 2.24 TW 3,4-23,9 кВт (закрытая камера сгорания)</t>
   </si>
 </sst>
 </file>
@@ -17962,8 +17968,18 @@
       </c>
     </row>
     <row r="604" spans="3:6">
-      <c r="D604" s="7"/>
-      <c r="F604" s="9"/>
+      <c r="C604" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D604" s="7">
+        <v>78142</v>
+      </c>
+      <c r="E604" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F604" s="9">
+        <v>46306</v>
+      </c>
     </row>
     <row r="605" spans="3:6">
       <c r="D605" s="7"/>
@@ -17996,7 +18012,7 @@
     <row r="612" spans="4:6">
       <c r="D612" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6473561.5600000015</v>
+        <v>6551703.5600000015</v>
       </c>
       <c r="F612" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="1019">
   <si>
     <t>№ п/п</t>
   </si>
@@ -4004,15 +4004,45 @@
   <si>
     <t>котёл газовый двухконтурный Haier TechLine S 2.24 TW 3,4-23,9 кВт (закрытая камера сгорания)</t>
   </si>
+  <si>
+    <t>вывоз мусора</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Авито Семён</t>
+  </si>
+  <si>
+    <t>прокат - аренда пресс клещей Valtec</t>
+  </si>
+  <si>
+    <t>тройник-пресс D20 sempiter icma 5 шт</t>
+  </si>
+  <si>
+    <t>тройник канализационный D50/50 mm угол 45 ртп</t>
+  </si>
+  <si>
+    <t>гильза медная лужённая гмл 10-5 10 шт.\упак DORI</t>
+  </si>
+  <si>
+    <t>Колено канализационное d50мм угол 45° РТП</t>
+  </si>
+  <si>
+    <t>труба канализационная 50 х 250 х 1,8 мм РТП</t>
+  </si>
+  <si>
+    <t>крестовина канализационная одноплоскостная D110/50/50 mm угол 90, РТП</t>
+  </si>
+  <si>
+    <t>труба канализационная 50х500х1,8 мм ртп</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4368,17 +4398,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4392,9 +4422,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4432,11 +4462,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4481,9 +4511,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4503,7 +4533,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4514,7 +4544,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4523,7 +4553,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4556,49 +4586,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4625,10 +4655,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4709,7 +4739,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4982,8 +5012,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F612" totalsRowCount="1">
-  <autoFilter ref="B5:F611"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F629" totalsRowCount="1">
+  <autoFilter ref="B5:F628"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -7924,7 +7954,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I612"/>
+  <dimension ref="B3:I629"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="94.7109375" customWidth="1"/>
@@ -17982,39 +18012,206 @@
       </c>
     </row>
     <row r="605" spans="3:6">
-      <c r="D605" s="7"/>
-      <c r="F605" s="9"/>
+      <c r="D605" s="7">
+        <v>1039</v>
+      </c>
+      <c r="E605" t="s">
+        <v>885</v>
+      </c>
+      <c r="F605" s="9">
+        <v>46307</v>
+      </c>
     </row>
     <row r="606" spans="3:6">
-      <c r="D606" s="7"/>
-      <c r="F606" s="9"/>
+      <c r="C606" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D606" s="7">
+        <v>10000</v>
+      </c>
+      <c r="E606" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F606" s="9">
+        <v>46307</v>
+      </c>
     </row>
     <row r="607" spans="3:6">
-      <c r="D607" s="7"/>
-      <c r="F607" s="9"/>
+      <c r="C607" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D607" s="7">
+        <v>400</v>
+      </c>
+      <c r="E607" t="s">
+        <v>885</v>
+      </c>
+      <c r="F607" s="9">
+        <v>46308</v>
+      </c>
     </row>
     <row r="608" spans="3:6">
-      <c r="D608" s="7"/>
-      <c r="F608" s="9"/>
-    </row>
-    <row r="609" spans="4:6">
-      <c r="D609" s="7"/>
-      <c r="F609" s="9"/>
-    </row>
-    <row r="610" spans="4:6">
-      <c r="D610" s="7"/>
-      <c r="F610" s="9"/>
-    </row>
-    <row r="611" spans="4:6">
-      <c r="D611" s="7"/>
-      <c r="F611" s="9"/>
-    </row>
-    <row r="612" spans="4:6">
+      <c r="C608" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D608" s="7">
+        <f>5*789</f>
+        <v>3945</v>
+      </c>
+      <c r="E608" t="s">
+        <v>885</v>
+      </c>
+      <c r="F608" s="9">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="609" spans="3:6">
+      <c r="C609" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D609" s="7">
+        <v>75</v>
+      </c>
+      <c r="E609" t="s">
+        <v>885</v>
+      </c>
+      <c r="F609" s="9">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="610" spans="3:6">
+      <c r="C610" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D610" s="7">
+        <v>319</v>
+      </c>
+      <c r="E610" t="s">
+        <v>885</v>
+      </c>
+      <c r="F610" s="9">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="611" spans="3:6">
+      <c r="C611" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D611" s="7">
+        <v>44</v>
+      </c>
+      <c r="E611" t="s">
+        <v>885</v>
+      </c>
+      <c r="F611" s="9">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="612" spans="3:6">
+      <c r="C612" t="s">
+        <v>1016</v>
+      </c>
       <c r="D612" s="7">
+        <v>69</v>
+      </c>
+      <c r="E612" t="s">
+        <v>885</v>
+      </c>
+      <c r="F612" s="9">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="613" spans="3:6">
+      <c r="C613" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D613" s="7">
+        <v>419</v>
+      </c>
+      <c r="E613" t="s">
+        <v>885</v>
+      </c>
+      <c r="F613" s="9">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="614" spans="3:6">
+      <c r="C614" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D614" s="7">
+        <f>2*93</f>
+        <v>186</v>
+      </c>
+      <c r="E614" t="s">
+        <v>885</v>
+      </c>
+      <c r="F614" s="9">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="615" spans="3:6">
+      <c r="D615" s="7"/>
+      <c r="F615" s="9"/>
+    </row>
+    <row r="616" spans="3:6">
+      <c r="D616" s="7"/>
+      <c r="F616" s="9"/>
+    </row>
+    <row r="617" spans="3:6">
+      <c r="D617" s="7"/>
+      <c r="F617" s="9"/>
+    </row>
+    <row r="618" spans="3:6">
+      <c r="D618" s="7"/>
+      <c r="F618" s="9"/>
+    </row>
+    <row r="619" spans="3:6">
+      <c r="D619" s="7"/>
+      <c r="F619" s="9"/>
+    </row>
+    <row r="620" spans="3:6">
+      <c r="D620" s="7"/>
+      <c r="F620" s="9"/>
+    </row>
+    <row r="621" spans="3:6">
+      <c r="D621" s="7"/>
+      <c r="F621" s="9"/>
+    </row>
+    <row r="622" spans="3:6">
+      <c r="D622" s="7"/>
+      <c r="F622" s="9"/>
+    </row>
+    <row r="623" spans="3:6">
+      <c r="D623" s="7"/>
+      <c r="F623" s="9"/>
+    </row>
+    <row r="624" spans="3:6">
+      <c r="D624" s="7"/>
+      <c r="F624" s="9"/>
+    </row>
+    <row r="625" spans="4:6">
+      <c r="D625" s="7"/>
+      <c r="F625" s="9"/>
+    </row>
+    <row r="626" spans="4:6">
+      <c r="D626" s="7"/>
+      <c r="F626" s="9"/>
+    </row>
+    <row r="627" spans="4:6">
+      <c r="D627" s="7"/>
+      <c r="F627" s="9"/>
+    </row>
+    <row r="628" spans="4:6">
+      <c r="D628" s="7"/>
+      <c r="F628" s="9"/>
+    </row>
+    <row r="629" spans="4:6">
+      <c r="D629" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6551703.5600000015</v>
-      </c>
-      <c r="F612" s="9"/>
+        <v>6568199.5600000015</v>
+      </c>
+      <c r="F629" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="1021">
   <si>
     <t>№ п/п</t>
   </si>
@@ -4034,15 +4034,21 @@
   <si>
     <t>труба канализационная 50х500х1,8 мм ртп</t>
   </si>
+  <si>
+    <t>труба металлопластиковая pex-al-pex 20x2 valtec 24 метра</t>
+  </si>
+  <si>
+    <t>калибр для металлопластиковой трубы 16-20-26 с ножами для снятия фаски Valtec</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4398,17 +4404,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4422,9 +4428,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4462,11 +4468,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4511,9 +4517,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4533,7 +4539,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4544,7 +4550,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4553,7 +4559,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4586,49 +4592,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4655,10 +4661,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4739,7 +4745,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -18151,12 +18157,33 @@
       </c>
     </row>
     <row r="615" spans="3:6">
-      <c r="D615" s="7"/>
-      <c r="F615" s="9"/>
+      <c r="C615" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D615" s="7">
+        <f>161.23*24</f>
+        <v>3869.5199999999995</v>
+      </c>
+      <c r="E615" t="s">
+        <v>885</v>
+      </c>
+      <c r="F615" s="9">
+        <v>46311</v>
+      </c>
     </row>
     <row r="616" spans="3:6">
-      <c r="D616" s="7"/>
-      <c r="F616" s="9"/>
+      <c r="C616" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D616" s="7">
+        <v>205.54</v>
+      </c>
+      <c r="E616" t="s">
+        <v>885</v>
+      </c>
+      <c r="F616" s="9">
+        <v>46311</v>
+      </c>
     </row>
     <row r="617" spans="3:6">
       <c r="D617" s="7"/>
@@ -18209,7 +18236,7 @@
     <row r="629" spans="4:6">
       <c r="D629" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6568199.5600000015</v>
+        <v>6572274.620000001</v>
       </c>
       <c r="F629" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="1021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="1026">
   <si>
     <t>№ п/п</t>
   </si>
@@ -4040,15 +4040,30 @@
   <si>
     <t>калибр для металлопластиковой трубы 16-20-26 с ножами для снятия фаски Valtec</t>
   </si>
+  <si>
+    <t>рулетка 5м х 25 мм  Dorn + пружина для металлопласт 16 и 20 мм</t>
+  </si>
+  <si>
+    <t>Эмаль-спрей акриловая color art 520ml ral7024 - 2 шт</t>
+  </si>
+  <si>
+    <t>шайба оцинк  м8 - 20шт</t>
+  </si>
+  <si>
+    <t>болт с шестигран головкой оцинк м8х50мм 8шт</t>
+  </si>
+  <si>
+    <t>коронка bi-metal 8% по металлу/дереву 102мм dorn  pro</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4404,17 +4419,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4428,9 +4443,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4468,11 +4483,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4517,9 +4532,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4539,7 +4554,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4550,7 +4565,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4559,7 +4574,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4592,49 +4607,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4661,10 +4676,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4745,7 +4760,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -18018,6 +18033,9 @@
       </c>
     </row>
     <row r="605" spans="3:6">
+      <c r="C605" t="s">
+        <v>1021</v>
+      </c>
       <c r="D605" s="7">
         <v>1039</v>
       </c>
@@ -18186,24 +18204,76 @@
       </c>
     </row>
     <row r="617" spans="3:6">
-      <c r="D617" s="7"/>
-      <c r="F617" s="9"/>
+      <c r="C617" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D617" s="7">
+        <f>255.23 * 2</f>
+        <v>510.46</v>
+      </c>
+      <c r="E617" t="s">
+        <v>885</v>
+      </c>
+      <c r="F617" s="9">
+        <v>46314</v>
+      </c>
     </row>
     <row r="618" spans="3:6">
-      <c r="D618" s="7"/>
-      <c r="F618" s="9"/>
+      <c r="C618" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D618" s="7">
+        <v>65.87</v>
+      </c>
+      <c r="E618" t="s">
+        <v>885</v>
+      </c>
+      <c r="F618" s="9">
+        <v>46314</v>
+      </c>
     </row>
     <row r="619" spans="3:6">
-      <c r="D619" s="7"/>
-      <c r="F619" s="9"/>
+      <c r="C619" t="s">
+        <v>805</v>
+      </c>
+      <c r="D619" s="7">
+        <v>72.27</v>
+      </c>
+      <c r="E619" t="s">
+        <v>885</v>
+      </c>
+      <c r="F619" s="9">
+        <v>46314</v>
+      </c>
     </row>
     <row r="620" spans="3:6">
-      <c r="D620" s="7"/>
-      <c r="F620" s="9"/>
+      <c r="C620" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D620" s="7">
+        <f>52.15 * 2</f>
+        <v>104.3</v>
+      </c>
+      <c r="E620" t="s">
+        <v>885</v>
+      </c>
+      <c r="F620" s="9">
+        <v>46314</v>
+      </c>
     </row>
     <row r="621" spans="3:6">
-      <c r="D621" s="7"/>
-      <c r="F621" s="9"/>
+      <c r="C621" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D621" s="7">
+        <v>997.12</v>
+      </c>
+      <c r="E621" t="s">
+        <v>885</v>
+      </c>
+      <c r="F621" s="9">
+        <v>46314</v>
+      </c>
     </row>
     <row r="622" spans="3:6">
       <c r="D622" s="7"/>
@@ -18236,7 +18306,7 @@
     <row r="629" spans="4:6">
       <c r="D629" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6572274.620000001</v>
+        <v>6574024.6400000006</v>
       </c>
       <c r="F629" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="1026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="1030">
   <si>
     <t>№ п/п</t>
   </si>
@@ -4055,15 +4055,27 @@
   <si>
     <t>коронка bi-metal 8% по металлу/дереву 102мм dorn  pro</t>
   </si>
+  <si>
+    <t>Гайка DIN934 шестигранная оцинк. М8 Кл. проч.8.0 80шт</t>
+  </si>
+  <si>
+    <t>Анкер хим. д/средних нагрузок, полиэстер, 300мл TYTAN</t>
+  </si>
+  <si>
+    <t>выравнивание участака - аренда трактора jcb</t>
+  </si>
+  <si>
+    <t>Павел Бойнарович  +7981 459 42 80</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4419,17 +4431,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4443,9 +4455,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4483,11 +4495,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4532,9 +4544,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4554,7 +4566,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4565,7 +4577,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4574,7 +4586,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4607,49 +4619,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4676,10 +4688,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4760,7 +4772,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -18276,37 +18288,77 @@
       </c>
     </row>
     <row r="622" spans="3:6">
-      <c r="D622" s="7"/>
-      <c r="F622" s="9"/>
+      <c r="C622" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D622" s="7">
+        <v>222.96</v>
+      </c>
+      <c r="E622" t="s">
+        <v>885</v>
+      </c>
+      <c r="F622" s="9">
+        <v>46315</v>
+      </c>
     </row>
     <row r="623" spans="3:6">
-      <c r="D623" s="7"/>
-      <c r="F623" s="9"/>
+      <c r="C623" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D623" s="7">
+        <v>805</v>
+      </c>
+      <c r="E623" t="s">
+        <v>885</v>
+      </c>
+      <c r="F623" s="9">
+        <v>46315</v>
+      </c>
     </row>
     <row r="624" spans="3:6">
-      <c r="D624" s="7"/>
-      <c r="F624" s="9"/>
-    </row>
-    <row r="625" spans="4:6">
-      <c r="D625" s="7"/>
-      <c r="F625" s="9"/>
-    </row>
-    <row r="626" spans="4:6">
+      <c r="C624" t="s">
+        <v>404</v>
+      </c>
+      <c r="D624" s="7">
+        <v>51.04</v>
+      </c>
+      <c r="E624" t="s">
+        <v>885</v>
+      </c>
+      <c r="F624" s="9">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="625" spans="3:6">
+      <c r="C625" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D625" s="7">
+        <v>16000</v>
+      </c>
+      <c r="E625" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F625" s="9">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="626" spans="3:6">
       <c r="D626" s="7"/>
       <c r="F626" s="9"/>
     </row>
-    <row r="627" spans="4:6">
+    <row r="627" spans="3:6">
       <c r="D627" s="7"/>
       <c r="F627" s="9"/>
     </row>
-    <row r="628" spans="4:6">
+    <row r="628" spans="3:6">
       <c r="D628" s="7"/>
       <c r="F628" s="9"/>
     </row>
-    <row r="629" spans="4:6">
+    <row r="629" spans="3:6">
       <c r="D629" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6574024.6400000006</v>
+        <v>6591103.6400000006</v>
       </c>
       <c r="F629" s="9"/>
     </row>

--- a/6-131.xlsx
+++ b/6-131.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Building\my_home\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zip\develop\my_home\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
     <sheet name="дерево заказ на 18 апр 2026" sheetId="15" r:id="rId15"/>
     <sheet name="расчёт кол-ва профилей оконных" sheetId="17" r:id="rId16"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="1030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="1037">
   <si>
     <t>№ п/п</t>
   </si>
@@ -4067,15 +4067,36 @@
   <si>
     <t>Павел Бойнарович  +7981 459 42 80</t>
   </si>
+  <si>
+    <t>диск отрезной по металлу и нержавеющей стали 3 шт</t>
+  </si>
+  <si>
+    <t>труба для дымохода из нержавеющей стали 0,6мм D80 L=50 см</t>
+  </si>
+  <si>
+    <t>труба канализационная D50 1m 3шт</t>
+  </si>
+  <si>
+    <t>Колено канализационное d50мм угол 45° РТП - 8шт</t>
+  </si>
+  <si>
+    <t>Муфта канализационная соединительная d110мм РТП - 2 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">пакет бауцентр большой </t>
+  </si>
+  <si>
+    <t>редукция канализационная 110/50 низкая РТП - 2 шт</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
   </numFmts>
   <fonts count="39">
     <font>
@@ -4431,17 +4452,17 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4455,9 +4476,9 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4495,11 +4516,11 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4544,9 +4565,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4566,7 +4587,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -4577,7 +4598,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4586,7 +4607,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -4619,49 +4640,49 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4688,10 +4709,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;₽&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4772,7 +4793,7 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;р.&quot;"/>
+      <numFmt numFmtId="165" formatCode="#,##0.00\ &quot;р.&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5045,8 +5066,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F629" totalsRowCount="1">
-  <autoFilter ref="B5:F628"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="B5:F642" totalsRowCount="1">
+  <autoFilter ref="B5:F641"/>
   <tableColumns count="5">
     <tableColumn id="1" name="№ п/п"/>
     <tableColumn id="2" name="Наименование "/>
@@ -7987,7 +8008,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I629"/>
+  <dimension ref="B3:I642"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="94.7109375" customWidth="1"/>
@@ -18344,23 +18365,145 @@
       </c>
     </row>
     <row r="626" spans="3:6">
-      <c r="D626" s="7"/>
-      <c r="F626" s="9"/>
+      <c r="C626" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D626" s="7">
+        <v>267</v>
+      </c>
+      <c r="E626" t="s">
+        <v>790</v>
+      </c>
+      <c r="F626" s="9">
+        <v>46318</v>
+      </c>
     </row>
     <row r="627" spans="3:6">
-      <c r="D627" s="7"/>
-      <c r="F627" s="9"/>
+      <c r="C627" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D627" s="7">
+        <v>590</v>
+      </c>
+      <c r="E627" t="s">
+        <v>790</v>
+      </c>
+      <c r="F627" s="9">
+        <v>46318</v>
+      </c>
     </row>
     <row r="628" spans="3:6">
-      <c r="D628" s="7"/>
-      <c r="F628" s="9"/>
+      <c r="C628" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D628" s="7">
+        <v>417</v>
+      </c>
+      <c r="E628" t="s">
+        <v>885</v>
+      </c>
+      <c r="F628" s="9">
+        <v>46318</v>
+      </c>
     </row>
     <row r="629" spans="3:6">
+      <c r="C629" t="s">
+        <v>1033</v>
+      </c>
       <c r="D629" s="7">
+        <v>352</v>
+      </c>
+      <c r="E629" t="s">
+        <v>885</v>
+      </c>
+      <c r="F629" s="9">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="630" spans="3:6">
+      <c r="C630" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D630" s="7">
+        <v>258</v>
+      </c>
+      <c r="E630" t="s">
+        <v>885</v>
+      </c>
+      <c r="F630" s="9">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="631" spans="3:6">
+      <c r="C631" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D631" s="7">
+        <v>9</v>
+      </c>
+      <c r="E631" t="s">
+        <v>885</v>
+      </c>
+      <c r="F631" s="9">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="632" spans="3:6">
+      <c r="C632" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D632" s="7">
+        <v>198</v>
+      </c>
+      <c r="E632" t="s">
+        <v>885</v>
+      </c>
+      <c r="F632" s="9">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="633" spans="3:6">
+      <c r="D633" s="7"/>
+      <c r="F633" s="9"/>
+    </row>
+    <row r="634" spans="3:6">
+      <c r="D634" s="7"/>
+      <c r="F634" s="9"/>
+    </row>
+    <row r="635" spans="3:6">
+      <c r="D635" s="7"/>
+      <c r="F635" s="9"/>
+    </row>
+    <row r="636" spans="3:6">
+      <c r="D636" s="7"/>
+      <c r="F636" s="9"/>
+    </row>
+    <row r="637" spans="3:6">
+      <c r="D637" s="7"/>
+      <c r="F637" s="9"/>
+    </row>
+    <row r="638" spans="3:6">
+      <c r="D638" s="7"/>
+      <c r="F638" s="9"/>
+    </row>
+    <row r="639" spans="3:6">
+      <c r="D639" s="7"/>
+      <c r="F639" s="9"/>
+    </row>
+    <row r="640" spans="3:6">
+      <c r="D640" s="7"/>
+      <c r="F640" s="9"/>
+    </row>
+    <row r="641" spans="4:6">
+      <c r="D641" s="7"/>
+      <c r="F641" s="9"/>
+    </row>
+    <row r="642" spans="4:6">
+      <c r="D642" s="7">
         <f>SUBTOTAL(109,Таблица4[Цена (руб)])</f>
-        <v>6591103.6400000006</v>
-      </c>
-      <c r="F629" s="9"/>
+        <v>6593194.6400000006</v>
+      </c>
+      <c r="F642" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
